--- a/Pre-contest Preparations/teams promoted into the international oral defense.xlsx
+++ b/Pre-contest Preparations/teams promoted into the international oral defense.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easonshao/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\stOOrz-Mathematical-Modelling-Group\IMMC_2022_Greater_China_Oral_Defense\Pre-contest Preparations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E82AB3-B097-0542-854E-36FC88C6E3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1800" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{9C2A7445-743B-5742-A5B2-8B1A104B01C0}"/>
+    <workbookView xWindow="5184" yWindow="1800" windowWidth="28044" windowHeight="17436"/>
   </bookViews>
   <sheets>
     <sheet name="中华赛" sheetId="1" r:id="rId1"/>
@@ -350,12 +349,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -372,12 +371,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="19"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -389,8 +382,39 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,6 +445,21 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -431,10 +470,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -445,18 +493,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -469,9 +514,21 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="4">
+    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="差" xfId="2" builtinId="27"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="适中" xfId="3" builtinId="28"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -782,15 +839,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D55CA7FF-1A68-474B-8183-F294E16E3856}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.1796875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="25">
+    <row r="1" spans="1:2" ht="25.2" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -798,482 +855,485 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="19">
+    <row r="2" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="19">
+    <row r="3" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="19">
+    <row r="4" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="19">
+    <row r="5" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="19">
+    <row r="6" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="19">
+    <row r="7" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="19">
+    <row r="8" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="19">
+    <row r="9" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="19">
+    <row r="10" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="19">
+    <row r="11" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="19">
+    <row r="12" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="19">
+    <row r="13" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="19">
+    <row r="14" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="19">
+    <row r="15" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="19">
+    <row r="16" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="19">
+    <row r="17" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="12" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="19">
+    <row r="18" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="19">
+    <row r="19" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="19">
+    <row r="20" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="19">
+    <row r="21" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="19">
+    <row r="22" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="19">
+    <row r="23" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="19">
+    <row r="24" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="19">
+    <row r="25" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="19">
+    <row r="26" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="19">
+    <row r="27" spans="1:2" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="12" t="s">
         <v>91</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD75162-1C75-A04B-AE1D-9D7B6813F75B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:3" ht="24.6" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2" spans="1:3" ht="19">
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="19">
+    <row r="3" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="19">
+    <row r="4" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="19">
+    <row r="5" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="19">
+    <row r="6" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="7"/>
-    </row>
-    <row r="7" spans="1:3" ht="19">
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="7"/>
-    </row>
-    <row r="8" spans="1:3" ht="19">
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="7"/>
-    </row>
-    <row r="9" spans="1:3" ht="19">
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="7"/>
-    </row>
-    <row r="10" spans="1:3" ht="19">
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:3" ht="19">
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" spans="1:3" ht="19">
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:3" ht="19">
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" spans="1:3" ht="19">
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15" spans="1:3" ht="19">
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:3" ht="19">
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" ht="19">
+      <c r="C16" s="6"/>
+    </row>
+    <row r="17" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3" ht="19">
+      <c r="C17" s="6"/>
+    </row>
+    <row r="18" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" ht="19">
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" ht="19">
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="7"/>
-    </row>
-    <row r="21" spans="1:3" ht="19">
+      <c r="C20" s="6"/>
+    </row>
+    <row r="21" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:3" ht="19">
+      <c r="C21" s="6"/>
+    </row>
+    <row r="22" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:3" ht="19">
+      <c r="C22" s="6"/>
+    </row>
+    <row r="23" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="7"/>
-    </row>
-    <row r="24" spans="1:3" ht="19">
+      <c r="C23" s="6"/>
+    </row>
+    <row r="24" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="7"/>
-    </row>
-    <row r="25" spans="1:3" ht="19">
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C25" s="7"/>
-    </row>
-    <row r="26" spans="1:3" ht="19">
+      <c r="C25" s="6"/>
+    </row>
+    <row r="26" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="7"/>
-    </row>
-    <row r="27" spans="1:3" ht="19">
+      <c r="C26" s="6"/>
+    </row>
+    <row r="27" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="7"/>
+      <c r="C27" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B27" xr:uid="{8AD75162-1C75-A04B-AE1D-9D7B6813F75B}"/>
+  <autoFilter ref="A1:B27"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Pre-contest Preparations/teams promoted into the international oral defense.xlsx
+++ b/Pre-contest Preparations/teams promoted into the international oral defense.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="5184" yWindow="1800" windowWidth="28044" windowHeight="17436"/>
+    <workbookView xWindow="5184" yWindow="1800" windowWidth="28044" windowHeight="17436" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="中华赛" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">国际赛!$A$1:$B$27</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1072,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
@@ -1080,7 +1080,7 @@
     <col min="3" max="3" width="11.1796875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24.6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="24.6" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1099,8 +1099,11 @@
       <c r="C2" s="7" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1110,8 +1113,11 @@
       <c r="C3" s="8" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1121,8 +1127,11 @@
       <c r="C4" s="9" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -1132,8 +1141,11 @@
       <c r="C5" s="10" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -1141,8 +1153,11 @@
         <v>21</v>
       </c>
       <c r="C6" s="6"/>
-    </row>
-    <row r="7" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -1150,8 +1165,11 @@
         <v>25</v>
       </c>
       <c r="C7" s="6"/>
-    </row>
-    <row r="8" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
@@ -1159,8 +1177,11 @@
         <v>29</v>
       </c>
       <c r="C8" s="6"/>
-    </row>
-    <row r="9" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
@@ -1168,8 +1189,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="6"/>
-    </row>
-    <row r="10" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>36</v>
       </c>
@@ -1177,8 +1201,11 @@
         <v>37</v>
       </c>
       <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -1186,8 +1213,11 @@
         <v>41</v>
       </c>
       <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>44</v>
       </c>
@@ -1195,8 +1225,11 @@
         <v>45</v>
       </c>
       <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>48</v>
       </c>
@@ -1204,8 +1237,11 @@
         <v>35</v>
       </c>
       <c r="C13" s="6"/>
-    </row>
-    <row r="14" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>50</v>
       </c>
@@ -1213,8 +1249,11 @@
         <v>51</v>
       </c>
       <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>54</v>
       </c>
@@ -1222,8 +1261,11 @@
         <v>55</v>
       </c>
       <c r="C15" s="6"/>
-    </row>
-    <row r="16" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>57</v>
       </c>
@@ -1231,8 +1273,11 @@
         <v>7</v>
       </c>
       <c r="C16" s="6"/>
-    </row>
-    <row r="17" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>60</v>
       </c>
@@ -1240,8 +1285,11 @@
         <v>61</v>
       </c>
       <c r="C17" s="6"/>
-    </row>
-    <row r="18" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>64</v>
       </c>
@@ -1249,8 +1297,11 @@
         <v>65</v>
       </c>
       <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>68</v>
       </c>
@@ -1258,8 +1309,11 @@
         <v>69</v>
       </c>
       <c r="C19" s="6"/>
-    </row>
-    <row r="20" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>72</v>
       </c>
@@ -1267,8 +1321,11 @@
         <v>73</v>
       </c>
       <c r="C20" s="6"/>
-    </row>
-    <row r="21" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>76</v>
       </c>
@@ -1276,8 +1333,11 @@
         <v>77</v>
       </c>
       <c r="C21" s="6"/>
-    </row>
-    <row r="22" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>79</v>
       </c>
@@ -1285,8 +1345,11 @@
         <v>80</v>
       </c>
       <c r="C22" s="6"/>
-    </row>
-    <row r="23" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>83</v>
       </c>
@@ -1294,8 +1357,11 @@
         <v>19</v>
       </c>
       <c r="C23" s="6"/>
-    </row>
-    <row r="24" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>86</v>
       </c>
@@ -1303,8 +1369,11 @@
         <v>87</v>
       </c>
       <c r="C24" s="6"/>
-    </row>
-    <row r="25" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>90</v>
       </c>
@@ -1312,8 +1381,11 @@
         <v>91</v>
       </c>
       <c r="C25" s="6"/>
-    </row>
-    <row r="26" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>94</v>
       </c>
@@ -1321,8 +1393,11 @@
         <v>95</v>
       </c>
       <c r="C26" s="6"/>
-    </row>
-    <row r="27" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="D26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>97</v>
       </c>
@@ -1330,10 +1405,14 @@
         <v>71</v>
       </c>
       <c r="C27" s="6"/>
+      <c r="D27">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B27"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Pre-contest Preparations/teams promoted into the international oral defense.xlsx
+++ b/Pre-contest Preparations/teams promoted into the international oral defense.xlsx
@@ -1072,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
@@ -1080,7 +1080,7 @@
     <col min="3" max="3" width="11.1796875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24.6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="24.6" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1099,11 +1099,8 @@
       <c r="C2" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1113,11 +1110,8 @@
       <c r="C3" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1127,11 +1121,8 @@
       <c r="C4" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -1141,11 +1132,8 @@
       <c r="C5" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -1153,11 +1141,8 @@
         <v>21</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -1165,11 +1150,8 @@
         <v>25</v>
       </c>
       <c r="C7" s="6"/>
-      <c r="D7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
@@ -1177,11 +1159,8 @@
         <v>29</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
@@ -1189,11 +1168,8 @@
         <v>33</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>36</v>
       </c>
@@ -1201,11 +1177,8 @@
         <v>37</v>
       </c>
       <c r="C10" s="6"/>
-      <c r="D10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -1213,11 +1186,8 @@
         <v>41</v>
       </c>
       <c r="C11" s="6"/>
-      <c r="D11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>44</v>
       </c>
@@ -1225,11 +1195,8 @@
         <v>45</v>
       </c>
       <c r="C12" s="6"/>
-      <c r="D12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>48</v>
       </c>
@@ -1237,11 +1204,8 @@
         <v>35</v>
       </c>
       <c r="C13" s="6"/>
-      <c r="D13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>50</v>
       </c>
@@ -1249,11 +1213,8 @@
         <v>51</v>
       </c>
       <c r="C14" s="6"/>
-      <c r="D14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>54</v>
       </c>
@@ -1261,11 +1222,8 @@
         <v>55</v>
       </c>
       <c r="C15" s="6"/>
-      <c r="D15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>57</v>
       </c>
@@ -1273,11 +1231,8 @@
         <v>7</v>
       </c>
       <c r="C16" s="6"/>
-      <c r="D16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>60</v>
       </c>
@@ -1285,11 +1240,8 @@
         <v>61</v>
       </c>
       <c r="C17" s="6"/>
-      <c r="D17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>64</v>
       </c>
@@ -1297,11 +1249,8 @@
         <v>65</v>
       </c>
       <c r="C18" s="6"/>
-      <c r="D18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>68</v>
       </c>
@@ -1309,11 +1258,8 @@
         <v>69</v>
       </c>
       <c r="C19" s="6"/>
-      <c r="D19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>72</v>
       </c>
@@ -1321,11 +1267,8 @@
         <v>73</v>
       </c>
       <c r="C20" s="6"/>
-      <c r="D20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>76</v>
       </c>
@@ -1333,11 +1276,8 @@
         <v>77</v>
       </c>
       <c r="C21" s="6"/>
-      <c r="D21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>79</v>
       </c>
@@ -1345,11 +1285,8 @@
         <v>80</v>
       </c>
       <c r="C22" s="6"/>
-      <c r="D22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>83</v>
       </c>
@@ -1357,11 +1294,8 @@
         <v>19</v>
       </c>
       <c r="C23" s="6"/>
-      <c r="D23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>86</v>
       </c>
@@ -1369,11 +1303,8 @@
         <v>87</v>
       </c>
       <c r="C24" s="6"/>
-      <c r="D24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>90</v>
       </c>
@@ -1381,11 +1312,8 @@
         <v>91</v>
       </c>
       <c r="C25" s="6"/>
-      <c r="D25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>94</v>
       </c>
@@ -1393,11 +1321,8 @@
         <v>95</v>
       </c>
       <c r="C26" s="6"/>
-      <c r="D26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:3" ht="19.2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>97</v>
       </c>
@@ -1405,9 +1330,6 @@
         <v>71</v>
       </c>
       <c r="C27" s="6"/>
-      <c r="D27">
-        <v>26</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B27"/>
